--- a/assets/docs/boq-jeddah.xlsx
+++ b/assets/docs/boq-jeddah.xlsx
@@ -3106,7 +3106,9 @@
         <v>25</v>
       </c>
       <c r="F3" s="34"/>
-      <c r="G3" s="38"/>
+      <c r="G3" s="38">
+        <f t="shared" ref="G3:G6" si="1">D3*F3</f>
+      </c>
       <c r="H3" s="40"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
@@ -3146,7 +3148,9 @@
         <v>25</v>
       </c>
       <c r="F4" s="34"/>
-      <c r="G4" s="38"/>
+      <c r="G4" s="38">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H4" s="40"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
@@ -3186,7 +3190,9 @@
         <v>25</v>
       </c>
       <c r="F5" s="34"/>
-      <c r="G5" s="38"/>
+      <c r="G5" s="38">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H5" s="40"/>
       <c r="I5" s="42"/>
       <c r="J5" s="42"/>
@@ -3226,7 +3232,9 @@
         <v>25</v>
       </c>
       <c r="F6" s="65"/>
-      <c r="G6" s="66"/>
+      <c r="G6" s="66">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H6" s="68"/>
       <c r="I6" s="42"/>
       <c r="J6" s="42"/>
@@ -3296,7 +3304,9 @@
         <v>25</v>
       </c>
       <c r="F8" s="34"/>
-      <c r="G8" s="38"/>
+      <c r="G8" s="38">
+        <f>D8*F8</f>
+      </c>
       <c r="H8" s="40"/>
       <c r="I8" s="42"/>
       <c r="J8" s="42"/>
@@ -3328,7 +3338,9 @@
       <c r="D9" s="60"/>
       <c r="E9" s="54"/>
       <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
+      <c r="G9" s="63">
+        <f>SUM(G3:G8)</f>
+      </c>
       <c r="H9" s="82"/>
       <c r="I9" s="84"/>
       <c r="J9" s="84"/>
@@ -3402,7 +3414,9 @@
         <v>22</v>
       </c>
       <c r="F11" s="44"/>
-      <c r="G11" s="57"/>
+      <c r="G11" s="57">
+        <f>D11*F11</f>
+      </c>
       <c r="H11" s="92"/>
       <c r="I11" s="84"/>
       <c r="J11" s="84"/>
@@ -3434,7 +3448,9 @@
       <c r="D12" s="54"/>
       <c r="E12" s="54"/>
       <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
+      <c r="G12" s="63">
+        <f>G11</f>
+      </c>
       <c r="H12" s="82"/>
       <c r="I12" s="84"/>
       <c r="J12" s="84"/>
@@ -3508,7 +3524,9 @@
         <v>22</v>
       </c>
       <c r="F14" s="44"/>
-      <c r="G14" s="57"/>
+      <c r="G14" s="57">
+        <f>D14*F14</f>
+      </c>
       <c r="H14" s="92"/>
       <c r="I14" s="84"/>
       <c r="J14" s="84"/>
@@ -3540,7 +3558,9 @@
       <c r="D15" s="60"/>
       <c r="E15" s="54"/>
       <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
+      <c r="G15" s="63">
+        <f>G14</f>
+      </c>
       <c r="H15" s="82"/>
       <c r="I15" s="84"/>
       <c r="J15" s="84"/>
@@ -3614,7 +3634,9 @@
         <v>43</v>
       </c>
       <c r="F17" s="99"/>
-      <c r="G17" s="100"/>
+      <c r="G17" s="100">
+        <f>D17*F17</f>
+      </c>
       <c r="H17" s="48"/>
       <c r="I17" s="84"/>
       <c r="J17" s="84"/>
@@ -3646,7 +3668,9 @@
       <c r="D18" s="60"/>
       <c r="E18" s="54"/>
       <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
+      <c r="G18" s="63">
+        <f>G17</f>
+      </c>
       <c r="H18" s="82"/>
       <c r="I18" s="84"/>
       <c r="J18" s="84"/>
@@ -3720,7 +3744,9 @@
         <v>43</v>
       </c>
       <c r="F20" s="99"/>
-      <c r="G20" s="100"/>
+      <c r="G20" s="100">
+        <f t="shared" ref="G20:G21" si="2">D20*F20</f>
+      </c>
       <c r="H20" s="48"/>
     </row>
     <row r="21" ht="121.5" customHeight="1">
@@ -3740,7 +3766,9 @@
         <v>43</v>
       </c>
       <c r="F21" s="99"/>
-      <c r="G21" s="100"/>
+      <c r="G21" s="100">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H21" s="92"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -3752,7 +3780,9 @@
       <c r="D22" s="60"/>
       <c r="E22" s="54"/>
       <c r="F22" s="63"/>
-      <c r="G22" s="63"/>
+      <c r="G22" s="63">
+        <f>SUM(G20:G21)</f>
+      </c>
       <c r="H22" s="82"/>
       <c r="I22" s="84"/>
       <c r="J22" s="84"/>
@@ -3784,7 +3814,9 @@
       <c r="D23" s="90"/>
       <c r="E23" s="87"/>
       <c r="F23" s="87"/>
-      <c r="G23" s="93"/>
+      <c r="G23" s="93">
+        <f>G9+G12+G15+G18+G22</f>
+      </c>
       <c r="H23" s="104"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -10739,7 +10771,9 @@
         <v>22</v>
       </c>
       <c r="F3" s="30"/>
-      <c r="G3" s="33"/>
+      <c r="G3" s="33">
+        <f t="shared" ref="G3:G19" si="1">D3*F3</f>
+      </c>
       <c r="H3" s="35"/>
     </row>
     <row r="4" ht="135.0" customHeight="1">
@@ -10759,7 +10793,9 @@
         <v>22</v>
       </c>
       <c r="F4" s="43"/>
-      <c r="G4" s="44"/>
+      <c r="G4" s="44">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H4" s="45"/>
       <c r="J4" s="46"/>
       <c r="K4" s="47"/>
@@ -10795,7 +10831,9 @@
         <v>22</v>
       </c>
       <c r="F5" s="44"/>
-      <c r="G5" s="57"/>
+      <c r="G5" s="57">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H5" s="48"/>
     </row>
     <row r="6" ht="160.5" customHeight="1">
@@ -10815,7 +10853,9 @@
         <v>22</v>
       </c>
       <c r="F6" s="43"/>
-      <c r="G6" s="33"/>
+      <c r="G6" s="33">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H6" s="45"/>
       <c r="J6" s="46"/>
       <c r="K6" s="47"/>
@@ -10851,7 +10891,9 @@
         <v>22</v>
       </c>
       <c r="F7" s="44"/>
-      <c r="G7" s="57"/>
+      <c r="G7" s="57">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H7" s="48"/>
     </row>
     <row r="8" ht="184.5" customHeight="1">
@@ -10871,7 +10913,9 @@
         <v>22</v>
       </c>
       <c r="F8" s="30"/>
-      <c r="G8" s="33"/>
+      <c r="G8" s="33">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H8" s="35"/>
     </row>
     <row r="9" ht="123.75" customHeight="1">
@@ -10891,7 +10935,9 @@
         <v>43</v>
       </c>
       <c r="F9" s="44"/>
-      <c r="G9" s="57"/>
+      <c r="G9" s="57">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H9" s="48"/>
     </row>
     <row r="10" ht="127.5" customHeight="1">
@@ -10911,7 +10957,9 @@
         <v>46</v>
       </c>
       <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
+      <c r="G10" s="77">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H10" s="78"/>
       <c r="I10" s="80"/>
       <c r="J10" s="80"/>
@@ -10951,7 +10999,9 @@
         <v>22</v>
       </c>
       <c r="F11" s="44"/>
-      <c r="G11" s="57"/>
+      <c r="G11" s="57">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H11" s="48" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10973,7 +11023,9 @@
         <v>22</v>
       </c>
       <c r="F12" s="44"/>
-      <c r="G12" s="57"/>
+      <c r="G12" s="57">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H12" s="48" t="e">
         <v>#VALUE!</v>
       </c>
@@ -10995,7 +11047,9 @@
         <v>22</v>
       </c>
       <c r="F13" s="44"/>
-      <c r="G13" s="57"/>
+      <c r="G13" s="57">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H13" s="48" t="e">
         <v>#VALUE!</v>
       </c>
@@ -11017,7 +11071,9 @@
         <v>22</v>
       </c>
       <c r="F14" s="44"/>
-      <c r="G14" s="57"/>
+      <c r="G14" s="57">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H14" s="48" t="e">
         <v>#VALUE!</v>
       </c>
@@ -11039,7 +11095,9 @@
         <v>43</v>
       </c>
       <c r="F15" s="44"/>
-      <c r="G15" s="57"/>
+      <c r="G15" s="57">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H15" s="48" t="e">
         <v>#VALUE!</v>
       </c>
@@ -11061,7 +11119,9 @@
         <v>43</v>
       </c>
       <c r="F16" s="44"/>
-      <c r="G16" s="57"/>
+      <c r="G16" s="57">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H16" s="48" t="e">
         <v>#VALUE!</v>
       </c>
@@ -11083,7 +11143,9 @@
         <v>22</v>
       </c>
       <c r="F17" s="30"/>
-      <c r="G17" s="33"/>
+      <c r="G17" s="33">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H17" s="35" t="e">
         <v>#VALUE!</v>
       </c>
@@ -11105,7 +11167,9 @@
         <v>22</v>
       </c>
       <c r="F18" s="30"/>
-      <c r="G18" s="33"/>
+      <c r="G18" s="33">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H18" s="35" t="e">
         <v>#VALUE!</v>
       </c>
@@ -11127,7 +11191,9 @@
         <v>69</v>
       </c>
       <c r="F19" s="44"/>
-      <c r="G19" s="57"/>
+      <c r="G19" s="57">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H19" s="48" t="e">
         <v>#VALUE!</v>
       </c>
@@ -11141,7 +11207,9 @@
       <c r="D20" s="60"/>
       <c r="E20" s="54"/>
       <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
+      <c r="G20" s="63">
+        <f>SUM(G3:G19)</f>
+      </c>
       <c r="H20" s="94"/>
       <c r="I20" s="84"/>
       <c r="J20" s="84"/>
@@ -11215,7 +11283,9 @@
         <v>22</v>
       </c>
       <c r="F22" s="30"/>
-      <c r="G22" s="33"/>
+      <c r="G22" s="33">
+        <f t="shared" ref="G22:G26" si="2">D22*F22</f>
+      </c>
       <c r="H22" s="35" t="e">
         <v>#VALUE!</v>
       </c>
@@ -11257,7 +11327,9 @@
         <v>22</v>
       </c>
       <c r="F23" s="30"/>
-      <c r="G23" s="33"/>
+      <c r="G23" s="33">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H23" s="35" t="e">
         <v>#VALUE!</v>
       </c>
@@ -11299,7 +11371,9 @@
         <v>22</v>
       </c>
       <c r="F24" s="30"/>
-      <c r="G24" s="33"/>
+      <c r="G24" s="33">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H24" s="35" t="e">
         <v>#VALUE!</v>
       </c>
@@ -11341,7 +11415,9 @@
         <v>22</v>
       </c>
       <c r="F25" s="44"/>
-      <c r="G25" s="33"/>
+      <c r="G25" s="33">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H25" s="48" t="e">
         <v>#VALUE!</v>
       </c>
@@ -11363,7 +11439,9 @@
         <v>22</v>
       </c>
       <c r="F26" s="30"/>
-      <c r="G26" s="33"/>
+      <c r="G26" s="33">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H26" s="35" t="e">
         <v>#VALUE!</v>
       </c>
@@ -11397,7 +11475,9 @@
       <c r="D27" s="60"/>
       <c r="E27" s="54"/>
       <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
+      <c r="G27" s="63">
+        <f>SUM(G22:G26)</f>
+      </c>
       <c r="H27" s="94"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -11409,7 +11489,9 @@
       <c r="D28" s="90"/>
       <c r="E28" s="87"/>
       <c r="F28" s="87"/>
-      <c r="G28" s="93"/>
+      <c r="G28" s="93">
+        <f>G20+G27</f>
+      </c>
       <c r="H28" s="101"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
@@ -15403,7 +15485,9 @@
         <v>22</v>
       </c>
       <c r="F3" s="30"/>
-      <c r="G3" s="33"/>
+      <c r="G3" s="33">
+        <f t="shared" ref="G3:G7" si="1">D3*F3</f>
+      </c>
       <c r="H3" s="35" t="e">
         <v>#VALUE!</v>
       </c>
@@ -15445,7 +15529,9 @@
         <v>22</v>
       </c>
       <c r="F4" s="30"/>
-      <c r="G4" s="33"/>
+      <c r="G4" s="33">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H4" s="35" t="e">
         <v>#VALUE!</v>
       </c>
@@ -15487,7 +15573,9 @@
         <v>22</v>
       </c>
       <c r="F5" s="30"/>
-      <c r="G5" s="33"/>
+      <c r="G5" s="33">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H5" s="35" t="e">
         <v>#VALUE!</v>
       </c>
@@ -15529,7 +15617,9 @@
         <v>22</v>
       </c>
       <c r="F6" s="30"/>
-      <c r="G6" s="33"/>
+      <c r="G6" s="33">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H6" s="48" t="e">
         <v>#VALUE!</v>
       </c>
@@ -15571,7 +15661,9 @@
         <v>22</v>
       </c>
       <c r="F7" s="30"/>
-      <c r="G7" s="33"/>
+      <c r="G7" s="33">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H7" s="35" t="e">
         <v>#VALUE!</v>
       </c>
@@ -15605,7 +15697,9 @@
       <c r="D8" s="60"/>
       <c r="E8" s="54"/>
       <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
+      <c r="G8" s="63">
+        <f>SUM(G3:G7)</f>
+      </c>
       <c r="H8" s="63"/>
     </row>
     <row r="9">
@@ -15659,7 +15753,9 @@
         <v>22</v>
       </c>
       <c r="F10" s="44"/>
-      <c r="G10" s="57"/>
+      <c r="G10" s="57">
+        <f t="shared" ref="G10:G13" si="2">D10*F10</f>
+      </c>
       <c r="H10" s="57" t="e">
         <v>#VALUE!</v>
       </c>
@@ -15681,7 +15777,9 @@
         <v>22</v>
       </c>
       <c r="F11" s="44"/>
-      <c r="G11" s="57"/>
+      <c r="G11" s="57">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H11" s="48" t="e">
         <v>#VALUE!</v>
       </c>
@@ -15703,7 +15801,9 @@
         <v>22</v>
       </c>
       <c r="F12" s="30"/>
-      <c r="G12" s="33"/>
+      <c r="G12" s="33">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H12" s="35" t="e">
         <v>#VALUE!</v>
       </c>
@@ -15725,7 +15825,9 @@
         <v>22</v>
       </c>
       <c r="F13" s="44"/>
-      <c r="G13" s="33"/>
+      <c r="G13" s="33">
+        <f t="shared" si="2"/>
+      </c>
       <c r="H13" s="57" t="e">
         <v>#VALUE!</v>
       </c>
@@ -15739,7 +15841,9 @@
       <c r="D14" s="60"/>
       <c r="E14" s="54"/>
       <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
+      <c r="G14" s="63">
+        <f>SUM(G10:G13)</f>
+      </c>
       <c r="H14" s="63"/>
     </row>
     <row r="15">
@@ -15751,7 +15855,9 @@
       <c r="D15" s="90"/>
       <c r="E15" s="87"/>
       <c r="F15" s="87"/>
-      <c r="G15" s="93"/>
+      <c r="G15" s="93">
+        <f>G8+G14</f>
+      </c>
       <c r="H15" s="93"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -18812,7 +18918,9 @@
         <v>43</v>
       </c>
       <c r="F3" s="44"/>
-      <c r="G3" s="57"/>
+      <c r="G3" s="57">
+        <f t="shared" ref="G3:G10" si="1">D3*F3</f>
+      </c>
       <c r="H3" s="78"/>
     </row>
     <row r="4" ht="111.75" customHeight="1">
@@ -18832,7 +18940,9 @@
         <v>22</v>
       </c>
       <c r="F4" s="30"/>
-      <c r="G4" s="33"/>
+      <c r="G4" s="33">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H4" s="33"/>
     </row>
     <row r="5" ht="111.75" customHeight="1">
@@ -18852,7 +18962,9 @@
         <v>22</v>
       </c>
       <c r="F5" s="30"/>
-      <c r="G5" s="33"/>
+      <c r="G5" s="33">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H5" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -18874,7 +18986,9 @@
         <v>69</v>
       </c>
       <c r="F6" s="44"/>
-      <c r="G6" s="57"/>
+      <c r="G6" s="57">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H6" s="57" t="e">
         <v>#VALUE!</v>
       </c>
@@ -18896,7 +19010,9 @@
         <v>43</v>
       </c>
       <c r="F7" s="44"/>
-      <c r="G7" s="57"/>
+      <c r="G7" s="57">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H7" s="48" t="e">
         <v>#VALUE!</v>
       </c>
@@ -18918,7 +19034,9 @@
         <v>22</v>
       </c>
       <c r="F8" s="30"/>
-      <c r="G8" s="33"/>
+      <c r="G8" s="33">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H8" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -18940,7 +19058,9 @@
         <v>22</v>
       </c>
       <c r="F9" s="43"/>
-      <c r="G9" s="33"/>
+      <c r="G9" s="33">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H9" s="45" t="e">
         <v>#VALUE!</v>
       </c>
@@ -18979,7 +19099,9 @@
         <v>22</v>
       </c>
       <c r="F10" s="44"/>
-      <c r="G10" s="57"/>
+      <c r="G10" s="57">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H10" s="57" t="e">
         <v>#VALUE!</v>
       </c>
@@ -18993,7 +19115,9 @@
       <c r="D11" s="60"/>
       <c r="E11" s="54"/>
       <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
+      <c r="G11" s="63">
+        <f>SUM(G3:G10)</f>
+      </c>
       <c r="H11" s="63"/>
     </row>
     <row r="12">
@@ -19047,7 +19171,9 @@
         <v>69</v>
       </c>
       <c r="F13" s="30"/>
-      <c r="G13" s="33"/>
+      <c r="G13" s="33">
+        <f>D13*F13</f>
+      </c>
       <c r="H13" s="33" t="e">
         <v>#VALUE!</v>
       </c>
@@ -19061,7 +19187,9 @@
       <c r="D14" s="60"/>
       <c r="E14" s="54"/>
       <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
+      <c r="G14" s="63">
+        <f>G13</f>
+      </c>
       <c r="H14" s="63"/>
     </row>
     <row r="15">
@@ -19073,7 +19201,9 @@
       <c r="D15" s="90"/>
       <c r="E15" s="87"/>
       <c r="F15" s="87"/>
-      <c r="G15" s="93"/>
+      <c r="G15" s="93">
+        <f>G11+G14</f>
+      </c>
       <c r="H15" s="93"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -23119,7 +23249,9 @@
         <v>69</v>
       </c>
       <c r="F3" s="44"/>
-      <c r="G3" s="57"/>
+      <c r="G3" s="57">
+        <f>IFERROR(D3*F3,0)</f>
+      </c>
       <c r="H3" s="57"/>
       <c r="I3" s="18"/>
       <c r="J3" s="18"/>
@@ -23159,7 +23291,9 @@
         <v>69</v>
       </c>
       <c r="F4" s="43"/>
-      <c r="G4" s="57"/>
+      <c r="G4" s="57">
+        <f>D4*F4</f>
+      </c>
       <c r="H4" s="110"/>
       <c r="J4" s="111"/>
       <c r="K4" s="112"/>
@@ -23187,7 +23321,9 @@
       <c r="D5" s="60"/>
       <c r="E5" s="54"/>
       <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
+      <c r="G5" s="63">
+        <f>SUM(G3:G4)</f>
+      </c>
       <c r="H5" s="63"/>
     </row>
     <row r="6">
@@ -23241,7 +23377,9 @@
         <v>22</v>
       </c>
       <c r="F7" s="30"/>
-      <c r="G7" s="33"/>
+      <c r="G7" s="33">
+        <f t="shared" ref="G7:G8" si="1">D7*F7</f>
+      </c>
       <c r="H7" s="33"/>
     </row>
     <row r="8" ht="135.75" customHeight="1">
@@ -23261,7 +23399,9 @@
         <v>22</v>
       </c>
       <c r="F8" s="30"/>
-      <c r="G8" s="33"/>
+      <c r="G8" s="33">
+        <f t="shared" si="1"/>
+      </c>
       <c r="H8" s="33"/>
     </row>
     <row r="9">
@@ -23273,7 +23413,9 @@
       <c r="D9" s="60"/>
       <c r="E9" s="54"/>
       <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
+      <c r="G9" s="63">
+        <f>SUM(G7:G8)</f>
+      </c>
       <c r="H9" s="63"/>
     </row>
     <row r="10">
@@ -23327,7 +23469,9 @@
         <v>22</v>
       </c>
       <c r="F11" s="30"/>
-      <c r="G11" s="33"/>
+      <c r="G11" s="33">
+        <f>D11*F11</f>
+      </c>
       <c r="H11" s="33"/>
     </row>
     <row r="12">
@@ -23339,7 +23483,9 @@
       <c r="D12" s="60"/>
       <c r="E12" s="54"/>
       <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
+      <c r="G12" s="63">
+        <f>SUM(G10:G11)</f>
+      </c>
       <c r="H12" s="63"/>
     </row>
     <row r="13">
@@ -23393,7 +23539,9 @@
         <v>22</v>
       </c>
       <c r="F14" s="30"/>
-      <c r="G14" s="33"/>
+      <c r="G14" s="33">
+        <f>D14*F14</f>
+      </c>
       <c r="H14" s="33"/>
       <c r="I14" s="18"/>
       <c r="J14" s="18"/>
@@ -23425,7 +23573,9 @@
       <c r="D15" s="60"/>
       <c r="E15" s="54"/>
       <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
+      <c r="G15" s="63">
+        <f>SUM(G13:G14)</f>
+      </c>
       <c r="H15" s="63"/>
     </row>
     <row r="16">
@@ -23479,7 +23629,9 @@
         <v>22</v>
       </c>
       <c r="F17" s="44"/>
-      <c r="G17" s="57"/>
+      <c r="G17" s="57">
+        <f>D17*F17</f>
+      </c>
       <c r="H17" s="57"/>
     </row>
     <row r="18">
@@ -23491,7 +23643,9 @@
       <c r="D18" s="60"/>
       <c r="E18" s="54"/>
       <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
+      <c r="G18" s="63">
+        <f>SUM(G17)</f>
+      </c>
       <c r="H18" s="63"/>
     </row>
     <row r="19">
@@ -23503,7 +23657,9 @@
       <c r="D19" s="90"/>
       <c r="E19" s="87"/>
       <c r="F19" s="87"/>
-      <c r="G19" s="93"/>
+      <c r="G19" s="93">
+        <f>G5+G9+G12+G15+G18</f>
+      </c>
       <c r="H19" s="101"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
